--- a/Employee_Reports_wi48/Miguelito Costelo Mainit Q0434.xlsx
+++ b/Employee_Reports_wi48/Miguelito Costelo Mainit Q0434.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1264,11 +1264,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1313,11 +1313,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1362,11 +1362,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1411,11 +1411,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1448,11 +1448,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1497,11 +1497,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1547,11 +1547,11 @@
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-31</v>
+        <v>-34</v>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -1596,11 +1596,11 @@
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-31</v>
+        <v>-34</v>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -1645,11 +1645,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1682,11 +1682,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1731,11 +1731,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -1780,11 +1780,11 @@
         </is>
       </c>
       <c r="H28" s="3" t="n">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -1829,11 +1829,11 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -1852,9 +1852,21 @@
           <t>Procedure For Handling New or Unfamilliar Task (SOPs)</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr"/>
-      <c r="D30" s="3" t="inlineStr"/>
-      <c r="E30" s="3" t="inlineStr"/>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>LSME-IMS-SOP-022</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
           <t>04-May-2026</t>
@@ -1866,11 +1878,11 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -1915,11 +1927,11 @@
         </is>
       </c>
       <c r="H31" s="3" t="n">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -1964,11 +1976,11 @@
         </is>
       </c>
       <c r="H32" s="5" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
@@ -2013,11 +2025,11 @@
         </is>
       </c>
       <c r="H33" s="5" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
@@ -2062,11 +2074,11 @@
         </is>
       </c>
       <c r="H34" s="5" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
@@ -2111,11 +2123,11 @@
         </is>
       </c>
       <c r="H35" s="3" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
@@ -2148,11 +2160,11 @@
         </is>
       </c>
       <c r="H36" s="3" t="n">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
@@ -2752,7 +2764,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7814</v>
+        <v>7811</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2781,7 +2793,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7919</v>
+        <v>7916</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2810,7 +2822,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7924</v>
+        <v>7921</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2839,7 +2851,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7924</v>
+        <v>7921</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2934,7 +2946,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7971</v>
+        <v>7968</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2963,7 +2975,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7971</v>
+        <v>7968</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2992,7 +3004,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7971</v>
+        <v>7968</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -3021,7 +3033,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7951</v>
+        <v>7948</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -3050,7 +3062,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7951</v>
+        <v>7948</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -3079,7 +3091,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7958</v>
+        <v>7955</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -3108,7 +3120,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7952</v>
+        <v>7949</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -3137,7 +3149,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7952</v>
+        <v>7949</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -3166,7 +3178,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7952</v>
+        <v>7949</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -3195,7 +3207,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7958</v>
+        <v>7955</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -3224,7 +3236,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7959</v>
+        <v>7956</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -3253,7 +3265,7 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7958</v>
+        <v>7955</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -3282,7 +3294,7 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7959</v>
+        <v>7956</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -3311,7 +3323,7 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7959</v>
+        <v>7956</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -3340,7 +3352,7 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>7951</v>
+        <v>7948</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -3369,7 +3381,7 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>7952</v>
+        <v>7949</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -3398,7 +3410,7 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>7952</v>
+        <v>7949</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -3427,7 +3439,7 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>7971</v>
+        <v>7968</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -3456,7 +3468,7 @@
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>7971</v>
+        <v>7968</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -3485,7 +3497,7 @@
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>7951</v>
+        <v>7948</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -3514,7 +3526,7 @@
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>7951</v>
+        <v>7948</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
